--- a/DocDesign/RandomTool/CommonConfig/GameConfig/Activity.xlsx
+++ b/DocDesign/RandomTool/CommonConfig/GameConfig/Activity.xlsx
@@ -40,10 +40,10 @@
     <t>活动名称</t>
   </si>
   <si>
-    <t>活动类型(1:单游戏  2:平台)</t>
-  </si>
-  <si>
-    <t>总开关(0:关闭  1:开)</t>
+    <t>活动类型</t>
+  </si>
+  <si>
+    <t>开启类型(0:不开启  1:单游戏  2:平台)</t>
   </si>
   <si>
     <t>活动准备时间(秒)</t>
@@ -82,7 +82,7 @@
     <t>Type</t>
   </si>
   <si>
-    <t>OpenSwitch</t>
+    <t>OpenType</t>
   </si>
   <si>
     <t>PrepareTime</t>
@@ -1116,7 +1116,8 @@
   <cols>
     <col min="1" max="1" width="25.8888888888889" style="1" customWidth="1"/>
     <col min="2" max="2" width="22.1111111111111" customWidth="1"/>
-    <col min="3" max="4" width="33.8888888888889" customWidth="1"/>
+    <col min="3" max="3" width="26.3333333333333" customWidth="1"/>
+    <col min="4" max="4" width="33.8888888888889" customWidth="1"/>
     <col min="5" max="9" width="22.6666666666667" customWidth="1"/>
     <col min="10" max="10" width="27" customWidth="1"/>
     <col min="11" max="11" width="25.6666666666667" customWidth="1"/>
@@ -1296,10 +1297,10 @@
         <v>31</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>31</v>
